--- a/output/北塩原村_村提供台帳の確認.xlsx
+++ b/output/北塩原村_村提供台帳の確認.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -162,6 +162,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +579,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>資料２－３の令和６・７年度の実績は、台帳でほぼ裏づけられました（令和７年度の月平均の利用者数の差は1人以内）。正本の実績表は他メンバー版の値のままで、34行が村の資料と違っていました。</t>
+          <t>資料２－３の令和６・７年度の実績は、台帳でほぼ裏づけられました（令和７年度の月平均の利用者数の差は1人以内）。正本の実績表と第４章の成果目標の基準値は他メンバー版の値のままで、35行が村の資料と違っていました。</t>
         </is>
       </c>
     </row>
@@ -593,7 +596,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>実績表34行を書き換え（令和６・７年度は資料２－３、令和８年度は台帳）、評価の文7段落を値から組み立て直し、注記5件を足しました。括弧内の見込量と、令和９〜11年度の見込量は直していません。</t>
+          <t>表35行を書き換え（実績表は令和６・７年度が資料２－３、令和８年度は台帳）、評価の文7段落を値から組み立て直し、注記7件を足しました。括弧内の見込量と、令和９〜11年度の見込量は直していません。</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,7 +1967,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>正本の実績表の書き換え（34行）</t>
+          <t>正本の実績表の書き換え（35行）</t>
         </is>
       </c>
     </row>
@@ -3611,6 +3614,45 @@
           <t>資料２－３</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ＤＫ-35</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成果目標（福祉施設から一般就労への移行等） 令和６年度末の就労定着支援事業の利用者数</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>１人</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>令和６年度末の就労定着支援事業の利用者数</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>０人</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>令和６年度末の就労定着支援事業の利用者数</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>資料２－３・台帳</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3627,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3639,7 +3681,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>評価の文の書き換え（7段落）と注記（5件）</t>
+          <t>評価の文の書き換え（7段落）と注記（7件）</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3930,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-139）】共同生活援助の利用者は、令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。見込量は村の判断によるものですので、置き直すかどうかを確認しています。</t>
+          <t>【村へ確認（Ｍ-139）】共同生活援助の利用者は、令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、表５-８の見込量は月12人日です。逆に、居宅介護（表５-５）と生活介護（表５-８）は見込量が実績を上回っています。見込量は村の判断によるものですので、現に利用している方の継続、新たな利用、利用の終了を一人ずつ積み上げて置き直すかどうかを確認しています。</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3974,51 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-136・Ｍ-138）】成年後見制度利用支援事業は、資料２－３では令和６・７年度とも利用が０人ですが、表６-３（成年後見制度利用支援事業の利用状況）は令和６年度２人、令和７年度３人としており、村の資料どうしで食い違うため、本表の値を改めずに確認しています（Ｍ-138）。排泄管理支援用具の令和７年度は、資料２－３は77件ですが、台帳の給付の決定は84か月分です（Ｍ-136）。</t>
+          <t>【村へ確認（Ｍ-136・Ｍ-138）】成年後見制度利用支援事業は、資料２－３では令和６・７年度とも利用が０人ですが、表６-３（成年後見制度利用支援事業の利用状況）は令和６年度２人、令和７年度３人としており、村の資料どうしで食い違うため、本表の値を改めずに確認しています（Ｍ-138）。排泄管理支援用具の令和７年度は、資料２－３は77件ですが、台帳の給付の決定は84か月分です（Ｍ-136）。令和８年度の72件は年度を通した給付の決定の月数であり、このうち９月分までの給付は36件、10月分以降の36件は決定済みでこれから給付されるものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ＤＫ-注６</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>第4章 福祉施設から一般就労への移行等（目標の本文の後）</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>（足す）</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-140）】令和６年度末の就労定着支援事業の利用者数は、資料２－３と村の給付の台帳のいずれでも０人であるため、１人から０人に改めました。国の基本指針の基準（令和６年度末の実績の1.47倍以上）によれば目標は０人となりますが、令和８年度の途中から１人が利用していることを踏まえ、目標値の２人は据え置いて確認しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ＤＫ-注７</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（4）表５-13の見込量の後</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>（足す）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-136）】計画相談支援の表５-12・表５-13の人数は、協議会資料（資料２－３）に合わせて、年度の中で利用した方の実人数で示しています。単位の欄は「人／月」ですが、毎月の請求で数えると月に６人から７人程度であり、他のサービスの「人／月」とは数え方が違います。国の基本指針は計画相談支援の見込量を月間の利用者数で示すこととしているため、数え方を確認のうえ、単位又は値を揃えます。</t>
         </is>
       </c>
     </row>
@@ -3951,7 +4037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3964,7 +4050,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>照会（5件）</t>
+          <t>照会（6件）</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4187,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。置き直す場合は、Ｍ-21（卒業予定の方の一覧）とあわせて当方で案をお作りします。</t>
+          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、見込量は月12人日です。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。置き直す場合は、Ｍ-21（卒業予定の方の一覧）とあわせて当方で案をお作りします。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4113,25 +4199,52 @@
     <row r="10" ht="160" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Ｍ-140</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>就労定着支援事業の利用者数の基準値と目標値</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>正本 第４章の成果目標の表は、令和６年度末の就労定着支援事業の利用者数を１人としておりましたが、資料２－３と給付の台帳のいずれでも令和６・７年度の利用は０人でしたので、０人に改めました。国の基本指針の基準（令和６年度末の実績の1.47倍以上）によれば目標は０人となります。令和８年度の途中から１人が利用しておられることを踏まえ、目標値（令和11年度末２人）を据え置くか、改めるかをご教示ください。あわせて、令和８年度に利用を始められた方が、福祉施設から一般就労に移行された方であるか（一般就労への移行者数の目標に関わります）をご教示ください。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="160" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>他メンバー</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>正本 第５章の実績の表（表５-４から表５-14まで及び表５-29）は、他メンバー版の値のままでしたが、令和８年10月10日にお伝えしたとおり、村が自立支援協議会に出した実績（資料２－３）と食い違っておりました。令和８年10月22日に村から給付の台帳のご提供があり、資料２－３の値が裏づけられましたので、令和６・７年度を資料２－３の値に、令和８年度を台帳の値に改め、評価の文も改めました（表の34行と評価の7段落）。他メンバー版の値に別の出所（村から直接受け取られた数値など）がある場合は、お知らせいただけますでしょうか。なお、台帳は利用者ごとの記録ですので、当方では原本を共有の場所に置かず、集計値だけを用いております。</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>正本 第５章の実績の表（表５-４から表５-14まで及び表５-29）は、他メンバー版の値のままでしたが、令和８年10月10日にお伝えしたとおり、村が自立支援協議会に出した実績（資料２－３）と食い違っておりました。令和８年10月22日に村から給付の台帳のご提供があり、資料２－３の値が裏づけられましたので、令和６・７年度を資料２－３の値に、令和８年度を台帳の値に改め、評価の文も改めました（表の35行と評価の7段落）。他メンバー版の値に別の出所（村から直接受け取られた数値など）がある場合は、お知らせいただけますでしょうか。なお、台帳は利用者ごとの記録ですので、当方では原本を共有の場所に置かず、集計値だけを用いております。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>

--- a/output/北塩原村_村提供台帳の確認.xlsx
+++ b/output/北塩原村_村提供台帳の確認.xlsx
@@ -2901,12 +2901,12 @@
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>―（0）人分</t>
+          <t>1（0）人分</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>―（0）人日分</t>
+          <t>3（0）人日分</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>―（0）人分</t>
+          <t>0.8（0）人分</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>―（0）人日分</t>
+          <t>1（0）人日分</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>―（2）人分</t>
+          <t>4（2）人分</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>資料２－３</t>
+          <t>資料２－３・台帳</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
+          <t>児童発達支援は、令和６年度及び令和７年度にそれぞれ１人の利用がありました。放課後等デイサービスは、令和７年度に月2.25人・6.75人日と、見込量（１人・２人日）を上回りました。保育所等訪問支援は、令和７年度に１人の利用がありました。障がい児相談支援は、令和６年度が２人、令和７年度が４人です。令和８年度は、年度途中までに児童発達支援に１人、保育所等訪問支援に１人、障がい児相談支援に４人の利用があります。医療的ケア児等コーディネーターについては、令和８年度に近隣町村との連携により配置しました。その他のサービスについては、利用がありませんでした。</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-137）】障がい児のサービスは、台帳のご提供がなかったため、令和８年度を「―」としています。児童発達支援、放課後等デイサービス、保育所等訪問支援及び障がい児相談支援の令和８年度の実績を確認しています。</t>
+          <t>【村へ確認（Ｍ-137・Ｍ-141）】令和８年度は、令和８年10月23日にご提供いただいた障がい児の台帳の値です（障がい児相談支援は実人数）。放課後等デイサービスの令和８年度は、台帳が見込みのみのため「―」としています（Ｍ-137）。また、令和７年度の児童発達支援（資料２－３は１人・２人日、台帳は０人）と障がい児相談支援（資料２－３は４人、台帳は３人）は、資料２－３と台帳が食い違うため、本表は資料２－３の値のまま確認しています（Ｍ-141）。</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4050,7 +4050,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>照会（6件）</t>
+          <t>照会（7件）</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>次のサービスは台帳のご提供がなく、令和６・７年度を資料２－３の値に改めたうえで、令和８年度を「―」としております。令和８年度の途中までの実績（利用者数と利用日数）をご教示ください。利用がない場合は、ないとお答えください。①就労移行支援、②就労継続支援Ａ型、③児童発達支援、④放課後等デイサービス、⑤保育所等訪問支援、⑥障がい児相談支援、⑦理解促進研修・啓発事業、⑧日常生活用具（介護・訓練支援用具、自立生活支援用具）、⑨日中一時支援事業、⑩福祉ホーム事業。このうち①は、第４章の成果目標（一般就労への移行）の見通しに関わります。</t>
+          <t>次のサービスは台帳のご提供がなく、令和６・７年度を資料２－３の値に改めたうえで、令和８年度を「―」としております。令和８年度の途中までの実績（利用者数と利用日数）をご教示ください。利用がない場合は、ないとお答えください。①就労移行支援、②就労継続支援Ａ型、③放課後等デイサービス（令和８年10月23日にご提供いただいた台帳は令和８年度が見込みのみでしたので、実績の月をお示しください）、④理解促進研修・啓発事業、⑤日常生活用具（介護・訓練支援用具、自立生活支援用具）、⑥日中一時支援事業、⑦福祉ホーム事業。このうち①は、第４章の成果目標（一般就労への移行）の見通しに関わります。児童発達支援、保育所等訪問支援及び障がい児相談支援は、令和８年10月23日の台帳により分かりましたので、お答えいただかなくて差し支えありません。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -4226,25 +4226,52 @@
     <row r="11" ht="160" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Ｍ-141</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>障がい児の台帳と協議会資料（資料２－３）の令和７年度の食い違い</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>令和８年10月23日に障がい児の台帳をご提供いただき、ありがとうございました。令和６年度は資料２－３と台帳が一致し、放課後等デイサービスの令和７年度（月2.25人）も一致しました。次の２点は食い違っておりますので、どちらを計画に載せるかご教示ください。①児童発達支援の令和７年度：資料２－３は１人・２人日、台帳は「実績なし」（０人）。令和７年３月分の請求の扱いなど、年度の区切りの違いによるものか。②障がい児相談支援の令和７年度：資料２－３は４人、台帳は３人。当方では、確認がとれるまで資料２－３の値を載せております。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="160" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>他メンバー</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>正本 第５章の実績の表（表５-４から表５-14まで及び表５-29）は、他メンバー版の値のままでしたが、令和８年10月10日にお伝えしたとおり、村が自立支援協議会に出した実績（資料２－３）と食い違っておりました。令和８年10月22日に村から給付の台帳のご提供があり、資料２－３の値が裏づけられましたので、令和６・７年度を資料２－３の値に、令和８年度を台帳の値に改め、評価の文も改めました（表の35行と評価の7段落）。他メンバー版の値に別の出所（村から直接受け取られた数値など）がある場合は、お知らせいただけますでしょうか。なお、台帳は利用者ごとの記録ですので、当方では原本を共有の場所に置かず、集計値だけを用いております。</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>

--- a/output/北塩原村_村提供台帳の確認.xlsx
+++ b/output/北塩原村_村提供台帳の確認.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>表35行を書き換え（実績表は令和６・７年度が資料２－３、令和８年度は台帳）、評価の文7段落を値から組み立て直し、注記7件を足しました。括弧内の見込量と、令和９〜11年度の見込量は直していません。</t>
+          <t>表35行を書き換え（実績表は令和６・７年度が資料２－３、令和８年度は台帳）、評価の文7段落を値から組み立て直し、注記8件を足しました。括弧内の見込量と、令和９〜11年度の見込量は直していません。</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3681,7 +3681,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>評価の文の書き換え（7段落）と注記（7件）</t>
+          <t>評価の文の書き換え（7段落）と注記（8件）</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-136・Ｍ-137）】第５章の実績の表（表５-４から表５-14まで及び表５-29）の令和６・７年度は、「障害福祉サービス等の見込量と実績」（令和８年５月25日、北塩原村障がい者自立支援協議会 資料２－３）の値です。令和８年度は、村の給付の台帳（令和８年10月22日にご提供いただいたもの）の実施月３月から６月まで（サービスにより９月まで）の月平均です（計画相談支援は実人数、排泄管理支援用具は給付の決定の月数）。居宅介護のサービス提供時間は台帳に記載がないため、令和８年度は「―」としています。台帳の年度の区切りと、計画相談支援の人数の数え方を確認しています（Ｍ-136）。台帳のご提供がなかったサービスで、令和６・７年度の値を改めたものは、令和８年度を「―」としています（Ｍ-137）。</t>
+          <t>【村へ確認（Ｍ-136・Ｍ-137）】第５章の実績の表（表５-４から表５-14まで及び表５-29）の令和６・７年度は、「障害福祉サービス等の見込量と実績」（令和８年５月25日、北塩原村障がい者自立支援協議会 資料２－３）の値です。令和８年度は、村の給付の台帳（令和８年10月22日にご提供いただいたもの）の実施月３月から６月まで（サービスにより９月まで）の月平均です（計画相談支援は実人数、排泄管理支援用具は給付の決定の月数）。令和８年度は年度途中の暫定値であり、サービスにより月数が違うため、通年の実績とは比べられません。居宅介護のサービス提供時間は台帳に記載がないため、令和８年度は「―」としています。台帳の年度の区切りと、計画相談支援の人数の数え方を確認しています（Ｍ-136）。台帳のご提供がなかったサービスで、令和６・７年度の値を改めたものは、令和８年度を「―」としています（Ｍ-137）。</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-139）】共同生活援助の利用者は、令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、表５-８の見込量は月12人日です。逆に、居宅介護（表５-５）と生活介護（表５-８）は見込量が実績を上回っています。見込量は村の判断によるものですので、現に利用している方の継続、新たな利用、利用の終了を一人ずつ積み上げて置き直すかどうかを確認しています。</t>
+          <t>【村へ確認（Ｍ-139）】共同生活援助の利用者は、令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、表５-８の見込量は月12人日です。短期入所（福祉型）は、利用は毎年度ありますが月２人日以下であり、見込量の月５人日を下回ります。逆に、居宅介護（表５-５）と生活介護（表５-８）は見込量が実績を上回っています。見込量は村の判断によるものですので、現に利用している方の継続、新たな利用、利用の終了を一人ずつ積み上げて置き直すかどうかを確認しています。</t>
         </is>
       </c>
     </row>
@@ -4003,20 +4003,42 @@
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>ＤＫ-注８</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>第5章1（5）表５-15の見込量の後</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>（足す）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-139）】児童発達支援の見込量（月８人日）は、実績（令和６年度 月５人日、令和７年度 月２人日、令和８年度 月３人日）を上回っています。保育所等訪問支援は令和８年度に利用があるため、令和９年度を０人とする理由を、障がい児相談支援は令和８年度の４人から３人に減る理由（18歳到達による計画相談支援への移行など）を、児童お一人ずつの見通しで確認しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>ＤＫ-注７</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>第5章1（4）表５-13の見込量の後</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>（足す）</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>【村へ確認（Ｍ-136）】計画相談支援の表５-12・表５-13の人数は、協議会資料（資料２－３）に合わせて、年度の中で利用した方の実人数で示しています。単位の欄は「人／月」ですが、毎月の請求で数えると月に６人から７人程度であり、他のサービスの「人／月」とは数え方が違います。国の基本指針は計画相談支援の見込量を月間の利用者数で示すこととしているため、数え方を確認のうえ、単位又は値を揃えます。</t>
         </is>
@@ -4187,7 +4209,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、見込量は月12人日です。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。置き直す場合は、Ｍ-21（卒業予定の方の一覧）とあわせて当方で案をお作りします。</t>
+          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、見込量は月12人日です。短期入所（福祉型）は、実績が月２人日以下（令和８年度は月１人日）であるのに対し、見込量は月５人日です。障がい児のサービスでは、児童発達支援の利用日数（実績 月２人日から５人日、令和８年度は月３人日）に対し見込量が月８人日、保育所等訪問支援は令和８年度に利用があるのに令和９年度の見込量が０人、障がい児相談支援は令和８年度の４人に対し見込量が３人です。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。置き直す場合は、Ｍ-21（卒業予定の方の一覧）とあわせて当方で案をお作りします。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/output/北塩原村_村提供台帳の確認.xlsx
+++ b/output/北塩原村_村提供台帳の確認.xlsx
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、見込量は月12人日です。短期入所（福祉型）は、実績が月２人日以下（令和８年度は月１人日）であるのに対し、見込量は月５人日です。障がい児のサービスでは、児童発達支援の利用日数（実績 月２人日から５人日、令和８年度は月３人日）に対し見込量が月８人日、保育所等訪問支援は令和８年度に利用があるのに令和９年度の見込量が０人、障がい児相談支援は令和８年度の４人に対し見込量が３人です。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。置き直す場合は、Ｍ-21（卒業予定の方の一覧）とあわせて当方で案をお作りします。</t>
+          <t>台帳によると、共同生活援助の利用者は令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令和９年度８人、令和10・11年度９人）を既に上回っています。逆に、居宅介護（令和８年度 月２人。見込量は令和９年度４人、令和10・11年度５人）と生活介護（同 月５人。見込量は令和９年度６人、令和10・11年度７人）は、見込量が実績を上回っています。自立訓練（生活訓練）も、令和８年度の月22人日に対し、見込量は月12人日です。短期入所（福祉型）は、実績が月２人日以下（令和８年度は月１人日）であるのに対し、見込量は月５人日です。障がい児のサービスでは、児童発達支援の利用日数（実績 月２人日から５人日、令和８年度は月３人日）に対し見込量が月８人日、保育所等訪問支援は令和８年度に利用があるのに令和９年度の見込量が０人、障がい児相談支援は令和８年度の４人に対し見込量が３人です。見込量は村のご判断によるものですので、置き直すかどうかをご教示ください。ご判断の材料として、いまの利用が続いた場合の参考値を当方でお作りしました（共同生活援助 月12人、居宅介護 月２人、生活介護 月５人など。卒業・年齢到達・地域移行による増減は含みません）。置き直す場合は、Ｍ-21（卒業予定の方の一覧）、Ｍ-15・Ｍ-20（年齢到達の一覧）の回答とあわせて、一人ずつの積上げに置き換えます。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
